--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260922.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.92%</t>
         </is>
       </c>
     </row>
@@ -667,88 +667,88 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>22,333,000</t>
+          <t>6,331,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,331,000</t>
+          <t>22,333,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>37,372,000</t>
+          <t>51,253,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>51,253,000</t>
+          <t>37,372,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,845,000</t>
+          <t>27,284,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>27,284,000</t>
+          <t>21,845,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>4,784,400</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -1188,29 +1188,29 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>4,784,400</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1232,117 +1232,117 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,818,461,204</t>
+          <t>17,775,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>17,775,000</t>
+          <t>2,837,381,204</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>6,795,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,795,000</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1606,24 +1606,24 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>54,146,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1657,39 +1657,39 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>54,146,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>17,681,000</t>
+          <t>20,037,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,22 +1701,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>20,037,000</t>
+          <t>17,681,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
